--- a/supplementary_data_2_runtime_governance_trace_logs.xlsx
+++ b/supplementary_data_2_runtime_governance_trace_logs.xlsx
@@ -34,20 +34,15 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +434,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14,989 patient encounters from cohort_v2_new0604.csv; AAS-positive 3,947; AAS-negative 11,042.</t>
+          <t>15,109 patient encounters from current_v2_dataset_ids0605.csv; AAS-positive 4,067; AAS-negative 11,042.</t>
         </is>
       </c>
     </row>
@@ -496,7 +499,7 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -505,7 +508,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,7 +646,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -670,7 +673,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Final V2 summary aligned to cohort_v2_new0604.csv.</t>
+          <t>Final V2 summary aligned to current_v2_dataset_ids0605.csv.</t>
         </is>
       </c>
     </row>
@@ -688,10 +691,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,11 +771,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Final submitted V2 rows use the latest CSV-defined patient set.</t>
+          <t>Final submitted V2 rows use the CSV-defined patient set.</t>
         </is>
       </c>
     </row>
@@ -789,7 +792,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1,071 / 14,989</t>
+          <t>1,071 / 15,109</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -812,20 +815,20 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -912,7 +915,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D2" t="n">
         <v>3871</v>
@@ -924,10 +927,10 @@
         <v>4175</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="H2" t="n">
-        <v>0.981</v>
+        <v>0.952</v>
       </c>
       <c r="I2" t="n">
         <v>0.622</v>
@@ -936,16 +939,16 @@
         <v>0.481</v>
       </c>
       <c r="K2" t="n">
-        <v>0.989</v>
+        <v>0.972</v>
       </c>
       <c r="L2" t="n">
-        <v>0.716</v>
+        <v>0.711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.646</v>
+        <v>0.639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.532</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="3">
@@ -960,10 +963,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D3" t="n">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="E3" t="n">
         <v>7680</v>
@@ -972,10 +975,10 @@
         <v>3362</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="H3" t="n">
-        <v>0.971</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0.696</v>
@@ -984,16 +987,16 @@
         <v>0.533</v>
       </c>
       <c r="K3" t="n">
-        <v>0.985</v>
+        <v>0.971</v>
       </c>
       <c r="L3" t="n">
-        <v>0.768</v>
+        <v>0.762</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.588</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1008,7 +1011,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D4" t="n">
         <v>3944</v>
@@ -1020,10 +1023,10 @@
         <v>3052</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.999</v>
+        <v>0.97</v>
       </c>
       <c r="I4" t="n">
         <v>0.724</v>
@@ -1032,16 +1035,16 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.796</v>
+        <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.721</v>
+        <v>0.713</v>
       </c>
       <c r="N4" t="n">
-        <v>0.638</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="5">
@@ -1056,7 +1059,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D5" t="n">
         <v>3866</v>
@@ -1068,10 +1071,10 @@
         <v>5556</v>
       </c>
       <c r="G5" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="H5" t="n">
-        <v>0.979</v>
+        <v>0.951</v>
       </c>
       <c r="I5" t="n">
         <v>0.497</v>
@@ -1080,16 +1083,16 @@
         <v>0.41</v>
       </c>
       <c r="K5" t="n">
-        <v>0.985</v>
+        <v>0.965</v>
       </c>
       <c r="L5" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="M5" t="n">
-        <v>0.578</v>
+        <v>0.573</v>
       </c>
       <c r="N5" t="n">
-        <v>0.434</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
@@ -1104,10 +1107,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D6" t="n">
-        <v>3653</v>
+        <v>3727</v>
       </c>
       <c r="E6" t="n">
         <v>4366</v>
@@ -1116,28 +1119,28 @@
         <v>6676</v>
       </c>
       <c r="G6" t="n">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="H6" t="n">
-        <v>0.926</v>
+        <v>0.916</v>
       </c>
       <c r="I6" t="n">
         <v>0.395</v>
       </c>
       <c r="J6" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="L6" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="M6" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="N6" t="n">
-        <v>0.305</v>
+        <v>0.299</v>
       </c>
     </row>
   </sheetData>
@@ -1219,28 +1222,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="I2" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
@@ -1250,28 +1253,28 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3" t="n">
         <v>11</v>
       </c>
-      <c r="C3" t="n">
-        <v>35</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I3" t="n">
-        <v>76</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
@@ -1281,28 +1284,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H4" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="I4" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -1312,28 +1315,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1350,9 +1353,9 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1380,7 +1383,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,071 / 14,989</t>
+          <t>1,071 / 15,109</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1419,7 +1422,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Terminal-action agreement after reassignment remained 83.4% in this subgroup.</t>
+          <t>Terminal-action agreement between canonical and multi-agent actions was 83.6% overall.</t>
         </is>
       </c>
     </row>

--- a/supplementary_data_2_runtime_governance_trace_logs.xlsx
+++ b/supplementary_data_2_runtime_governance_trace_logs.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="runtime_validity_summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="governance_audit_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="final_v2_route_metrics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="residual_fn_subtypes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="residual_fn_stanford" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deescalated_direct_cta" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -34,12 +34,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -60,11 +65,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15,109 patient encounters from current_v2_dataset_ids0605.csv; AAS-positive 4,067; AAS-negative 11,042.</t>
+          <t>15,109 patient encounters from current_v2_dataset_ids0605.csv; AD-positive 4,067; AD-negative 11,042.</t>
         </is>
       </c>
     </row>
@@ -797,7 +809,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Canonical direct-CTA cases reassigned to clinician-overseen reassessment; 0 AAS-positive cases in this subgroup.</t>
+          <t>Canonical direct-CTA cases reassigned to clinician-overseen reassessment; 0 AD-positive cases in this subgroup.</t>
         </is>
       </c>
     </row>
@@ -1154,189 +1166,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Stanford A</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Stanford B</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Intramural haematoma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Penetrating atherosclerotic ulcer</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Unphenotyped/indeterminate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Any type-A descriptor</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Worst-case type-A upper bound</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Unphenotyped/indeterminate AD</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Worst-case Stanford A upper bound</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Total false negatives</t>
         </is>
       </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ADD-RS &gt;=1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D2" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H2" t="n">
-        <v>52</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="E2" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>201</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Canonical</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="n">
-        <v>49</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="D3" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>53</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>196</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Single-agent</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="D4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="D4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G4" t="n">
-        <v>53</v>
-      </c>
-      <c r="H4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="E4" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Multi-agent</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>38</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="E5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>123</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Stanford A upper bound treats all unphenotyped/indeterminate AD residual reassessment records as Stanford A. The sheet reports AD-focused Stanford classification only.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1371,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAS-positive / AAS-negative in this subgroup</t>
+          <t>AD-positive / AD-negative in this subgroup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1405,7 +1381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reassignment reduced false-positive assigned escalation in retrospective policy simulation; no adjudicated AAS-positive patient was reassigned through this route.</t>
+          <t>Reassignment reduced false-positive assigned escalation in retrospective policy simulation; no adjudicated AD-positive patient was reassigned through this route.</t>
         </is>
       </c>
     </row>

--- a/supplementary_data_2_runtime_governance_trace_logs.xlsx
+++ b/supplementary_data_2_runtime_governance_trace_logs.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="final_v2_route_metrics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="residual_fn_stanford" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deescalated_direct_cta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="high_consequence_residual" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -494,6 +495,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>All V2 negative labels were individually confirmed by telephone follow-up during physician adjudication in May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>high_consequence_residual</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aggregate post hoc audit of conservative Stanford A-risk residual AD-positive reassessment assignments and prospective blocking-trigger implications; the 22-record denominator is 10 confirmed Stanford A plus 12 unphenotyped/indeterminate AD records, not 22 confirmed Stanford A cases; contains no patient identifiers or raw clinical text.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1201,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Stanford A</t>
+          <t>Confirmed Stanford A</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -1203,12 +1216,12 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Worst-case Stanford A upper bound</t>
+          <t>Worst-case Stanford A-risk upper bound</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Total false negatives</t>
+          <t>Total residual AD-positive reassessment</t>
         </is>
       </c>
       <c r="G1" s="1" t="n"/>
@@ -1311,7 +1324,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Stanford A upper bound treats all unphenotyped/indeterminate AD residual reassessment records as Stanford A. The sheet reports AD-focused Stanford classification only.</t>
+          <t>The Stanford A-risk upper bound treats all unphenotyped/indeterminate AD residual reassessment records as Stanford A for conservative safety accounting. It is not a count of confirmed Stanford A cases. The sheet reports AD-focused Stanford classification only.</t>
         </is>
       </c>
     </row>
@@ -1422,4 +1435,238 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Audit item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count / denominator</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Prospective blocking implication</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Conservative Stanford A-risk denominator</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22/123</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10 confirmed Stanford A plus 12 unphenotyped/indeterminate AD among multi-agent residual reassessment assignments; this is a worst-case upper bound, not 22 confirmed Stanford A cases.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Treat confirmed proximal or untyped AD evidence as a blocking trigger before accepting reassessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reviewable structured trace records</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21/22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Restricted pathway-trace fields were available for 21 of 22 conservative Stanford A-risk records; one confirmed Stanford A record lacked reviewable trace fields in the non-PHI audit export</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Missing trace evidence should be handled as an information gap, not as reassuring absence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Reconstructed ADD-RS equals 0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22/22 conservative Stanford A-risk records; 123/123 total multi-agent residual AD-positive records</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Submission-facing current rows had no reconstructed ADD-RS risk-domain points among residual reassessment assignments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Do not allow ADD-RS-zero or absent structured domains to produce silent non-escalation when AD remains clinically plausible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No documented classic-pain flag in structured trace</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21/21 reviewable conservative Stanford A-risk records</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trace fields did not record sudden, severe, tearing, or migrating pain flags in the reviewable conservative Stanford A-risk records</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Require physician acknowledgement when classic-pain fields are absent or undocumented in a still-suspicious presentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>No high-yield examination flag in structured trace</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21/21 reviewable conservative Stanford A-risk records</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trace fields did not record pulse deficit, BP differential, new aortic-regurgitation murmur, neurologic deficit, or shock flags</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Do not treat absent structured examination flags as autonomous rule-out; require active monitoring and override availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Terminal stage among reviewable conservative Stanford A-risk records</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CP1 14/21; CP2 1/21; CP4 6/21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Most reviewable conservative Stanford A-risk records terminated before later evidence modules</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Block early terminal reassessment when pain persists, critical fields are missing, or the clinician requests further evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D-dimer trace field among reviewable conservative Stanford A-risk records</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Unavailable/not recorded 14/21; available normal 6/21; abnormal 1/21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D-dimer did not consistently rescue conservative Stanford A-risk records in the trace audit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Missing or normal D-dimer should not override persistent suspicion or proximal-aortic concern; abnormal D-dimer with persistent symptoms should trigger imaging or senior review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Echo/proximal-aortic trace signal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Echo-suspicion signal 2/21; ascending-aortic dilation field positive 3/21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A minority of conservative Stanford A-risk records had available echo/proximal-aortic signal; most had no positive or unavailable echo signal in trace fields</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Any proximal-aortic or echo-suspicion evidence should block reassessment; absence or unavailability of echo evidence should not be used as reassurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Atypical or complex context flags</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Acute-primary 16/21; ambiguous 5/21; post-operative/unspecified 1/21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Conservative Stanford A-risk residuals were not limited to a single easy-to-exclude chronic or prior-intervention subgroup</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ambiguous, post-operative, follow-up, or prior-intervention contexts require specialist review rather than automatic reassessment.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>